--- a/data/export/2026-10-06-operations.xlsx
+++ b/data/export/2026-10-06-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1164,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1203,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1214,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1280,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1330,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1396,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1446,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1512,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1562,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1628,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1654,35 +1678,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1739,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1758,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1794,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1855,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1874,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1899,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1975,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1994,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2019,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2095,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2114,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2139,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2375,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2386,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2447,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2466,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2491,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2502,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2515,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2563,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2582,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,7 +2618,7 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -2595,22 +2631,22 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2679,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2698,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2734,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2795,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2814,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2850,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2911,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2930,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2966,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3027,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3046,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3082,2927 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-operations.xlsx
+++ b/data/export/2026-10-06-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD47"/>
+  <dimension ref="A1:AD72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1131,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1164,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1188,17 +1200,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1208,13 +1220,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1247,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1280,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1304,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1396,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1420,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1551,7 +1583,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1595,32 +1627,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1628,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1652,33 +1688,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1711,32 +1751,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1744,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1768,33 +1812,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1827,32 +1875,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1860,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1884,17 +1936,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1904,17 +1956,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1947,32 +1999,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1980,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2004,37 +2060,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2139,7 +2195,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2154,7 +2210,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,7 +2392,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2380,13 +2436,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2512,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2496,41 +2556,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2563,12 +2627,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2582,7 +2646,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2607,46 +2671,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2679,12 +2747,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2698,7 +2766,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2723,7 +2791,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2734,35 +2802,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2795,12 +2863,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2814,7 +2882,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2839,46 +2907,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2911,12 +2983,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2930,7 +3002,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2955,46 +3027,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3027,12 +3103,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3046,7 +3122,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3071,46 +3147,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3143,12 +3223,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3162,7 +3242,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3187,46 +3267,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>68.5</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3259,12 +3343,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3278,7 +3362,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3303,18 +3387,22 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3327,60 +3415,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3394,7 +3486,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3404,33 +3496,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3443,60 +3539,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3510,7 +3610,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3520,33 +3620,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3559,60 +3663,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3626,7 +3734,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3636,17 +3744,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3656,13 +3764,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3675,22 +3787,22 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3723,12 +3835,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3742,7 +3854,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3778,7 +3890,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3791,60 +3903,64 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3858,7 +3974,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3868,33 +3984,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3907,7 +4027,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3917,7 +4037,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3955,12 +4075,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3974,7 +4094,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4010,7 +4130,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4023,22 +4143,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4071,12 +4191,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4090,7 +4210,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4126,7 +4246,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4259,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4149,7 +4269,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4187,12 +4307,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4206,7 +4326,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4242,7 +4362,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4375,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4265,7 +4385,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4303,12 +4423,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4322,7 +4442,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4358,7 +4478,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4371,22 +4491,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4419,12 +4539,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4438,7 +4558,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4474,7 +4594,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4607,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4497,7 +4617,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4535,12 +4655,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4554,7 +4674,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4590,7 +4710,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4723,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4613,7 +4733,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4651,12 +4771,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4670,7 +4790,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4706,35 +4826,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4767,12 +4887,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4786,7 +4906,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4811,7 +4931,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4822,77 +4942,73 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4906,7 +5022,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4916,65 +5032,61 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5007,12 +5119,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5026,7 +5138,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5062,77 +5174,73 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5146,7 +5254,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5156,17 +5264,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5176,45 +5284,41 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5247,12 +5351,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5266,7 +5370,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5302,35 +5406,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5363,12 +5467,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5382,7 +5486,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5418,35 +5522,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5479,12 +5583,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5498,7 +5602,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5534,35 +5638,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5595,12 +5699,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5614,7 +5718,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5639,7 +5743,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5650,35 +5754,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5711,12 +5815,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5730,7 +5834,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5766,35 +5870,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5827,12 +5931,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5846,7 +5950,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5882,35 +5986,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5943,12 +6047,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5962,47 +6066,2999 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="W47" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X47" s="2" t="inlineStr">
+      <c r="X65" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y47" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z47" s="2" t="inlineStr">
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
+      <c r="AA65" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB47" s="2" t="inlineStr">
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="AD47" s="2" t="inlineStr">
-        <is>
-          <t>1/9</t>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-operations.xlsx
+++ b/data/export/2026-10-06-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD72"/>
+  <dimension ref="A1:AD96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2123,32 +2123,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2156,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2180,17 +2184,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,17 +2204,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2243,32 +2247,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2276,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2300,33 +2308,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2359,32 +2371,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2392,7 +2408,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2416,37 +2432,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2479,32 +2495,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2512,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2536,37 +2556,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2599,32 +2619,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2632,7 +2656,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2656,37 +2680,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2776,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2835,32 +2859,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2868,7 +2896,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2892,37 +2920,37 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2988,7 +3016,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3027,7 +3055,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3042,7 +3070,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3136,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3147,7 +3175,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3162,7 +3190,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3256,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3282,7 +3310,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3295,22 +3323,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3343,12 +3371,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3362,7 +3390,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3387,7 +3415,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3397,82 +3425,78 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3486,7 +3510,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3496,107 +3520,103 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3610,7 +3630,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3620,107 +3640,103 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3734,7 +3750,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3744,65 +3760,65 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3835,12 +3851,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3854,7 +3870,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3879,88 +3895,88 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3974,7 +3990,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3984,65 +4000,65 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4075,12 +4091,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4094,7 +4110,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4119,46 +4135,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4191,12 +4211,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4210,7 +4230,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4235,18 +4255,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4259,60 +4283,64 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4326,7 +4354,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4336,33 +4364,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4375,60 +4407,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4442,7 +4478,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4452,33 +4488,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4491,60 +4531,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4558,7 +4602,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4568,33 +4612,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4607,60 +4655,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4674,7 +4726,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4684,33 +4736,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4723,60 +4779,64 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4790,7 +4850,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4800,33 +4860,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4903,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4849,7 +4913,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4859,40 +4923,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4906,7 +4974,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4916,33 +4984,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4955,60 +5027,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5022,7 +5098,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5032,33 +5108,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5151,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5081,7 +5161,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5091,40 +5171,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5138,7 +5222,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5148,33 +5232,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5275,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5197,7 +5285,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5207,40 +5295,44 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5254,7 +5346,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5264,33 +5356,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5303,60 +5399,64 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5370,7 +5470,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5380,33 +5480,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5523,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5429,7 +5533,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5439,12 +5543,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5467,12 +5571,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5480,13 +5584,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
-      <c r="T42" s="2" t="inlineStr"/>
-      <c r="U42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 20分钟参与校验</t>
+        </is>
+      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5522,7 +5642,7 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5655,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5545,7 +5665,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5583,12 +5703,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5602,7 +5722,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5638,7 +5758,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5771,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5661,7 +5781,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5671,40 +5791,44 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5718,7 +5842,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5728,33 +5852,37 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5895,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5777,7 +5905,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5787,12 +5915,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq40推进至seq55，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5815,12 +5943,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5828,13 +5956,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
       <c r="T45" s="2" t="inlineStr"/>
-      <c r="U45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5870,7 +6010,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5883,22 +6023,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5931,12 +6071,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5950,7 +6090,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5986,7 +6126,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5999,7 +6139,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6009,7 +6149,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6047,12 +6187,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6066,7 +6206,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6102,7 +6242,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6115,22 +6255,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6163,12 +6303,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6182,7 +6322,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6218,7 +6358,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6371,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6241,7 +6381,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6279,12 +6419,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6298,7 +6438,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6334,7 +6474,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6487,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6357,7 +6497,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6395,12 +6535,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6414,7 +6554,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6450,7 +6590,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6603,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6473,7 +6613,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6511,12 +6651,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6530,7 +6670,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6555,22 +6695,18 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6583,22 +6719,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6636,7 +6772,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6650,7 +6786,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6675,22 +6811,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6703,22 +6835,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6751,12 +6883,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6770,7 +6902,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6806,7 +6938,7 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6951,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6829,7 +6961,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6872,7 +7004,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6886,7 +7018,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6911,50 +7043,46 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>126.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6987,12 +7115,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7006,7 +7134,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7031,7 +7159,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7042,77 +7170,73 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7126,7 +7250,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7136,65 +7260,61 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7227,12 +7347,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7246,7 +7366,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7271,7 +7391,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7282,77 +7402,73 @@
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7366,7 +7482,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7376,17 +7492,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7401,40 +7517,40 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7467,12 +7583,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7486,7 +7602,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7516,83 +7632,83 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7606,7 +7722,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7616,107 +7732,99 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7730,7 +7838,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7740,65 +7848,65 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7831,12 +7939,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7850,7 +7958,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7880,41 +7988,45 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7947,12 +8059,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7966,7 +8078,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7991,46 +8103,50 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8063,12 +8179,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8082,7 +8198,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8107,46 +8223,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8179,12 +8299,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8198,7 +8318,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8228,41 +8348,45 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8295,12 +8419,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8314,7 +8438,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8349,40 +8473,40 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8415,12 +8539,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8434,7 +8558,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8470,35 +8594,35 @@
       <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8531,12 +8655,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8550,7 +8674,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8585,40 +8709,40 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8651,12 +8775,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8670,7 +8794,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8695,46 +8819,50 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8767,12 +8895,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8786,7 +8914,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8816,13 +8944,17 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8967,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8845,7 +8977,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8888,7 +9020,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8902,7 +9034,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8927,7 +9059,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8942,7 +9074,7 @@
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8955,7 +9087,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8965,7 +9097,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8975,40 +9107,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9022,43 +9158,2943 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
+      <c r="X87" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z72" s="2" t="inlineStr">
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr"/>
-      <c r="AD72" s="2" t="inlineStr">
-        <is>
-          <t>—/12</t>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-operations.xlsx
+++ b/data/export/2026-10-06-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD112"/>
+  <dimension ref="A1:AD118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3501,24 +3501,24 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3735,32 +3735,36 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3768,7 +3772,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3792,17 +3796,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3812,12 +3816,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3888,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4008,7 +4012,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4047,7 +4051,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -4128,7 +4132,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4248,7 +4252,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4368,7 +4372,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4417,12 +4421,12 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4492,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4608,7 +4612,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4652,12 +4656,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
@@ -4669,70 +4673,66 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4756,22 +4756,22 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4781,82 +4781,78 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4870,7 +4866,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4880,37 +4876,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4919,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4933,7 +4929,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4953,12 +4949,12 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
@@ -4980,7 +4976,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4994,7 +4990,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5019,7 +5015,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -5029,12 +5025,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5047,24 +5043,24 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5077,24 +5073,24 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5104,7 +5100,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5118,7 +5114,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5153,12 +5149,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5171,24 +5167,24 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5201,24 +5197,24 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -5228,7 +5224,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5242,7 +5238,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5277,12 +5273,12 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5295,24 +5291,24 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5325,24 +5321,24 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5352,7 +5348,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5366,7 +5362,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5401,12 +5397,12 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5419,24 +5415,24 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>06:44</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5449,34 +5445,34 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5490,7 +5486,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5525,12 +5521,12 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5539,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5553,7 +5549,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5573,7 +5569,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5595,12 +5591,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5614,7 +5610,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5667,7 +5663,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5677,7 +5673,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5697,34 +5693,34 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5738,7 +5734,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5773,12 +5769,12 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5791,7 +5787,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5801,7 +5797,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5821,12 +5817,12 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
@@ -5843,12 +5839,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5862,7 +5858,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5897,12 +5893,12 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5915,60 +5911,64 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5976,29 +5976,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>物理seq22（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>07:58</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>08:04</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 20分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -6008,33 +5992,37 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6047,52 +6035,56 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6100,7 +6092,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6114,7 +6106,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6124,17 +6116,17 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6144,13 +6136,17 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6159,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6173,7 +6169,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6183,44 +6179,40 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6228,13 +6220,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr"/>
-      <c r="S47" s="2" t="inlineStr"/>
-      <c r="T47" s="2" t="inlineStr"/>
-      <c r="U47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 20分钟参与校验</t>
+        </is>
+      </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6244,37 +6252,33 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6287,32 +6291,32 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq40推进至seq61，推进21站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -6335,12 +6339,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6348,25 +6352,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>物理seq23（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>08:16</t>
-        </is>
-      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr"/>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6391,7 +6383,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6415,7 +6407,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6425,7 +6417,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6445,34 +6437,34 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6486,7 +6478,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6521,12 +6513,12 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6539,32 +6531,32 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq40推进至seq61，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -6587,12 +6579,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6600,13 +6592,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R50" s="2" t="inlineStr"/>
-      <c r="S50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
       <c r="T50" s="2" t="inlineStr"/>
-      <c r="U50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6631,7 +6635,7 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6655,24 +6659,24 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6685,29 +6689,29 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6726,7 +6730,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6761,12 +6765,12 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6779,64 +6783,60 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6860,17 +6860,17 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6880,17 +6880,13 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6899,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6913,7 +6909,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6933,7 +6929,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6945,22 +6941,22 @@
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6974,7 +6970,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -7027,7 +7023,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -7037,7 +7033,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -7057,29 +7053,29 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7098,7 +7094,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -7133,12 +7129,12 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7151,24 +7147,24 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7181,34 +7177,34 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7222,7 +7218,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7247,22 +7243,22 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -7275,24 +7271,24 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7305,34 +7301,34 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7346,7 +7342,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7371,22 +7367,22 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB56" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7399,24 +7395,24 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7429,19 +7425,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7470,7 +7466,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7505,12 +7501,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7523,60 +7519,64 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7590,7 +7590,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7600,33 +7600,37 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -7639,52 +7643,56 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7692,7 +7700,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7706,7 +7714,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7716,17 +7724,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7736,13 +7744,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7755,22 +7767,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7803,12 +7815,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7822,7 +7834,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7871,7 +7883,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7881,7 +7893,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7924,7 +7936,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7938,7 +7950,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7963,22 +7975,18 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7999,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -8001,7 +8009,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -8044,7 +8052,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8058,7 +8066,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -8083,22 +8091,18 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8115,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -8121,7 +8125,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -8159,12 +8163,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8178,7 +8182,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8203,18 +8207,22 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -8227,22 +8235,22 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8280,7 +8288,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8294,7 +8302,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8329,12 +8337,12 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -8347,22 +8355,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8395,12 +8403,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8414,7 +8422,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8439,22 +8447,18 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8471,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8477,7 +8481,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8520,7 +8524,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8534,7 +8538,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8569,12 +8573,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8591,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8597,7 +8601,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8640,7 +8644,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8654,7 +8658,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8689,12 +8693,12 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -8707,7 +8711,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8717,7 +8721,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8755,12 +8759,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8774,7 +8778,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8809,12 +8813,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8831,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8837,7 +8841,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8875,12 +8879,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8894,7 +8898,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8947,7 +8951,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A79307D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8957,7 +8961,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8995,12 +8999,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9014,7 +9018,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -9039,18 +9043,22 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9071,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -9073,7 +9081,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -9111,12 +9119,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9130,7 +9138,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9165,12 +9173,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9191,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9193,7 +9201,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9231,12 +9239,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9250,7 +9258,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9275,22 +9283,18 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9307,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9313,7 +9317,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9351,12 +9355,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9370,7 +9374,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9410,7 +9414,7 @@
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9427,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9433,7 +9437,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9471,12 +9475,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9490,7 +9494,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9520,13 +9524,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9547,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9549,7 +9557,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9587,12 +9595,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9606,7 +9614,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9641,12 +9649,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9667,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9669,7 +9677,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9707,12 +9715,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9726,7 +9734,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9775,22 +9783,22 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9823,7 +9831,7 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9842,7 +9850,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9877,12 +9885,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -9895,22 +9903,22 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9943,12 +9951,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9962,7 +9970,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9992,17 +10000,13 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10019,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -10025,7 +10029,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -10063,12 +10067,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10082,7 +10086,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -10135,7 +10139,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -10145,7 +10149,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -10183,7 +10187,7 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10202,7 +10206,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10237,40 +10241,40 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -10303,12 +10307,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10322,7 +10326,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10347,7 +10351,7 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
@@ -10357,82 +10361,78 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10446,7 +10446,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10456,65 +10456,65 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10566,7 +10566,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10601,82 +10601,78 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10690,7 +10686,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10700,37 +10696,37 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -10743,7 +10739,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10753,7 +10749,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10763,36 +10759,32 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10800,7 +10792,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10814,7 +10806,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10824,37 +10816,37 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10859,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10877,7 +10869,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10897,34 +10889,34 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10938,7 +10930,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10973,12 +10965,12 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -10991,7 +10983,7 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -11001,7 +10993,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -11011,44 +11003,40 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11062,7 +11050,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -11072,22 +11060,22 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
@@ -11097,12 +11085,12 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11103,7 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -11125,7 +11113,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -11145,34 +11133,34 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11186,7 +11174,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -11216,17 +11204,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11227,7 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -11249,7 +11237,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -11269,12 +11257,12 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
@@ -11291,12 +11279,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11310,7 +11298,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11340,17 +11328,17 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11363,7 +11351,7 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -11373,7 +11361,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -11393,34 +11381,34 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11434,7 +11422,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11459,17 +11447,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB90" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11487,24 +11475,24 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -11517,34 +11505,34 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11558,7 +11546,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11593,12 +11581,12 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11611,24 +11599,24 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -11641,19 +11629,19 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11663,12 +11651,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11682,7 +11670,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11707,22 +11695,22 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11735,24 +11723,24 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -11765,12 +11753,12 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
@@ -11787,12 +11775,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11806,7 +11794,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11841,12 +11829,12 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11859,24 +11847,24 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -11889,34 +11877,34 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11930,7 +11918,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11955,22 +11943,22 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11983,24 +11971,24 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12013,34 +12001,34 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12054,7 +12042,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -12079,7 +12067,7 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
@@ -12089,12 +12077,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12107,24 +12095,24 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12137,19 +12125,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -12159,12 +12147,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12178,7 +12166,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -12203,22 +12191,22 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB96" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -12231,24 +12219,24 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12261,34 +12249,34 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12302,7 +12290,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -12327,22 +12315,22 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -12355,24 +12343,24 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12385,12 +12373,12 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
@@ -12407,12 +12395,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12426,7 +12414,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -12451,22 +12439,22 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -12479,60 +12467,64 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12546,7 +12538,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -12556,17 +12548,17 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA99" s="2" t="inlineStr">
@@ -12576,13 +12568,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -12595,55 +12591,59 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12662,7 +12662,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12672,17 +12672,17 @@
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
@@ -12692,13 +12692,17 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC100" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -12711,60 +12715,64 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12778,7 +12786,7 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -12788,37 +12796,37 @@
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB101" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -12831,55 +12839,59 @@
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12898,7 +12910,7 @@
       <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
@@ -12908,22 +12920,22 @@
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
@@ -12933,12 +12945,12 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -12951,7 +12963,7 @@
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -12961,7 +12973,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -12999,12 +13011,12 @@
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13018,7 +13030,7 @@
       <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
@@ -13048,17 +13060,13 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC103" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -13071,60 +13079,64 @@
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr"/>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13138,7 +13150,7 @@
       <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
@@ -13148,37 +13160,37 @@
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -13191,22 +13203,22 @@
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -13239,12 +13251,12 @@
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13258,7 +13270,7 @@
       <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
@@ -13283,7 +13295,7 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
@@ -13293,12 +13305,12 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -13311,22 +13323,22 @@
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -13359,12 +13371,12 @@
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13378,7 +13390,7 @@
       <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
@@ -13403,22 +13415,22 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13443,7 @@
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -13441,7 +13453,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13479,12 +13491,12 @@
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13498,7 +13510,7 @@
       <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
@@ -13533,12 +13545,12 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -13551,22 +13563,22 @@
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -13599,12 +13611,12 @@
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13618,7 +13630,7 @@
       <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
@@ -13648,17 +13660,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -13671,22 +13683,22 @@
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -13719,12 +13731,12 @@
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13738,7 +13750,7 @@
       <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
@@ -13763,22 +13775,22 @@
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -13791,7 +13803,7 @@
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -13801,7 +13813,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -13839,12 +13851,12 @@
       <c r="N110" s="2" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -13858,7 +13870,7 @@
       <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
@@ -13883,18 +13895,22 @@
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB110" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -13907,22 +13923,22 @@
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -13955,12 +13971,12 @@
       <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -13974,7 +13990,7 @@
       <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
@@ -14009,12 +14025,12 @@
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -14027,7 +14043,7 @@
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -14037,7 +14053,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -14075,12 +14091,12 @@
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14094,43 +14110,763 @@
       <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" s="2" t="inlineStr">
         <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z112" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA112" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC112" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD112" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr"/>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr"/>
+      <c r="S113" s="2" t="inlineStr"/>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z113" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA113" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB113" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC113" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AD113" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr"/>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr"/>
+      <c r="S114" s="2" t="inlineStr"/>
+      <c r="T114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="W114" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z114" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA114" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC114" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD114" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr"/>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr"/>
+      <c r="S115" s="2" t="inlineStr"/>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z115" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA115" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC115" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD115" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr"/>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr"/>
+      <c r="S116" s="2" t="inlineStr"/>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z116" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA116" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC116" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD116" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr"/>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="W112" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr"/>
+      <c r="S117" s="2" t="inlineStr"/>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="W117" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X112" s="2" t="inlineStr">
+      <c r="X117" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y112" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z112" s="2" t="inlineStr">
+      <c r="Y117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z117" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA112" s="2" t="inlineStr">
+      <c r="AA117" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB112" s="2" t="inlineStr">
+      <c r="AB117" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC112" s="2" t="inlineStr"/>
-      <c r="AD112" s="2" t="inlineStr">
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="inlineStr">
         <is>
           <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr"/>
+      <c r="S118" s="2" t="inlineStr"/>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="W118" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z118" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA118" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC118" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD118" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-operations.xlsx
+++ b/data/export/2026-10-06-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2332,17 +2332,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3448,17 +3448,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5428,17 +5428,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7288,17 +7288,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7780,12 +7780,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8276,17 +8276,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9268,12 +9268,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9516,17 +9516,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -9693,12 +9693,12 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9931,32 +9931,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9964,7 +9968,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9988,17 +9992,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10008,12 +10012,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10051,32 +10055,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -10084,7 +10092,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10108,17 +10116,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -10128,12 +10136,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10171,32 +10179,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -10204,7 +10216,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10228,17 +10240,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10248,17 +10260,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10373,7 +10385,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10444,7 +10456,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10488,12 +10500,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
@@ -10746,7 +10758,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10828,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10860,17 +10872,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -11118,7 +11130,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11324,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11366,7 +11378,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11572,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11614,7 +11626,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11696,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11728,17 +11740,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -12064,7 +12076,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12108,17 +12120,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12196,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12320,7 +12332,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12364,17 +12376,17 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12452,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12688,7 +12700,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12732,12 +12744,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
@@ -12812,7 +12824,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12936,7 +12948,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -13060,7 +13072,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13109,12 +13121,12 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13250,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13374,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -13548,7 +13560,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13597,12 +13609,12 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -13726,7 +13738,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13986,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14056,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14168,7 +14180,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14212,17 +14224,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -14346,7 +14358,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14676,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14718,7 +14730,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15056,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15088,17 +15100,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -15168,7 +15180,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15222,7 +15234,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15304,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15336,17 +15348,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15552,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15584,17 +15596,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15676,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15912,7 +15924,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15956,12 +15968,12 @@
       </c>
       <c r="AB125" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
@@ -16036,7 +16048,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16160,7 +16172,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16462,7 +16474,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16544,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16710,7 +16722,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16970,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -17160,7 +17172,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17209,12 +17221,12 @@
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -17780,7 +17792,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17904,7 +17916,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17948,17 +17960,17 @@
       </c>
       <c r="AB141" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -18082,7 +18094,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18164,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18330,7 +18342,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18590,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -18702,7 +18714,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -19272,7 +19284,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19316,17 +19328,17 @@
       </c>
       <c r="AB152" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC152" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -19396,7 +19408,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19445,12 +19457,12 @@
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -19520,7 +19532,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19564,17 +19576,17 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19656,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19768,7 +19780,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19812,17 +19824,17 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -19892,7 +19904,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19936,12 +19948,12 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
@@ -20016,7 +20028,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20070,7 +20082,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20152,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20388,7 +20400,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20442,7 +20454,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -20636,7 +20648,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20938,7 +20950,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -21062,7 +21074,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -21508,7 +21520,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21605,24 +21617,24 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr"/>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
@@ -21632,7 +21644,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21681,12 +21693,12 @@
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -21719,32 +21731,36 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr"/>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N172" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -21752,7 +21768,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21776,17 +21792,17 @@
       </c>
       <c r="X172" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y172" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z172" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA172" s="2" t="inlineStr">
@@ -21796,17 +21812,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -21849,24 +21865,24 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
@@ -21876,7 +21892,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21925,12 +21941,12 @@
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -21963,32 +21979,36 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N174" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -21996,7 +22016,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22020,17 +22040,17 @@
       </c>
       <c r="X174" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y174" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z174" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA174" s="2" t="inlineStr">
@@ -22040,17 +22060,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -22083,12 +22103,12 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
@@ -22116,7 +22136,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22124,10 +22144,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R175" s="2" t="inlineStr"/>
-      <c r="S175" s="2" t="inlineStr"/>
-      <c r="T175" s="2" t="inlineStr"/>
-      <c r="U175" s="2" t="inlineStr"/>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V175" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -22203,32 +22239,36 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N176" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22236,7 +22276,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22260,17 +22300,17 @@
       </c>
       <c r="X176" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z176" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA176" s="2" t="inlineStr">
@@ -22280,17 +22320,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -22323,32 +22363,36 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N177" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -22356,7 +22400,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22380,17 +22424,17 @@
       </c>
       <c r="X177" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z177" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA177" s="2" t="inlineStr">
@@ -22400,17 +22444,17 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -22476,7 +22520,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22596,7 +22640,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22650,7 +22694,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -22683,32 +22727,36 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N180" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -22716,7 +22764,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22740,17 +22788,17 @@
       </c>
       <c r="X180" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA180" s="2" t="inlineStr">
@@ -22760,12 +22808,12 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
@@ -22836,7 +22884,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22956,7 +23004,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23010,7 +23058,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -23076,7 +23124,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23196,7 +23244,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23370,7 +23418,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -23494,7 +23542,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -23738,7 +23786,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -23932,7 +23980,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23981,12 +24029,12 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24282,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -24304,7 +24352,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24348,17 +24396,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -24428,7 +24476,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24472,17 +24520,17 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -24730,7 +24778,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -24800,7 +24848,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24844,17 +24892,17 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -24978,7 +25026,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -25296,7 +25344,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25345,12 +25393,12 @@
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -25540,7 +25588,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25584,17 +25632,17 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25712,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25708,17 +25756,17 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -25966,7 +26014,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -26036,7 +26084,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26080,17 +26128,17 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26262,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -26284,7 +26332,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26328,17 +26376,17 @@
       </c>
       <c r="AB209" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -26462,7 +26510,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -26776,7 +26824,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26825,12 +26873,12 @@
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -26900,7 +26948,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26944,17 +26992,17 @@
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -27024,7 +27072,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -27068,17 +27116,17 @@
       </c>
       <c r="AB215" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC215" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -27202,7 +27250,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -27272,7 +27320,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27316,17 +27364,17 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -27396,7 +27444,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27440,17 +27488,17 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -27818,7 +27866,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -27888,7 +27936,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27932,17 +27980,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -28132,7 +28180,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28176,17 +28224,17 @@
       </c>
       <c r="AB224" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -28256,7 +28304,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28300,17 +28348,17 @@
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -28504,7 +28552,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28548,12 +28596,12 @@
       </c>
       <c r="AB227" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
@@ -28682,7 +28730,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -29054,7 +29102,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -29124,7 +29172,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29168,17 +29216,17 @@
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -29248,7 +29296,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29292,17 +29340,17 @@
       </c>
       <c r="AB233" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -29372,7 +29420,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29416,12 +29464,12 @@
       </c>
       <c r="AB234" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC234" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD234" s="2" t="inlineStr">
@@ -29496,7 +29544,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29540,17 +29588,17 @@
       </c>
       <c r="AB235" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -29922,7 +29970,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -29992,7 +30040,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -30036,17 +30084,17 @@
       </c>
       <c r="AB239" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -30170,7 +30218,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -30364,7 +30412,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30408,17 +30456,17 @@
       </c>
       <c r="AB242" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC242" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -30488,7 +30536,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30537,12 +30585,12 @@
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -30612,7 +30660,7 @@
       </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q244" s="2" t="inlineStr">
@@ -30656,17 +30704,17 @@
       </c>
       <c r="AB244" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC244" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -30736,7 +30784,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30780,17 +30828,17 @@
       </c>
       <c r="AB245" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -30860,7 +30908,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
@@ -30904,17 +30952,17 @@
       </c>
       <c r="AB246" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC246" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -31108,7 +31156,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31152,12 +31200,12 @@
       </c>
       <c r="AB248" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
@@ -31410,7 +31458,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31582,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -31604,7 +31652,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31648,17 +31696,17 @@
       </c>
       <c r="AB252" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC252" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -31976,7 +32024,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32025,12 +32073,12 @@
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -32154,7 +32202,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -32224,7 +32272,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32268,17 +32316,17 @@
       </c>
       <c r="AB257" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC257" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -32344,7 +32392,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
@@ -32388,17 +32436,17 @@
       </c>
       <c r="AB258" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC258" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -32468,7 +32516,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32512,17 +32560,17 @@
       </c>
       <c r="AB259" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32640,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32636,12 +32684,12 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
@@ -33014,7 +33062,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -33084,7 +33132,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33128,17 +33176,17 @@
       </c>
       <c r="AB264" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -33262,7 +33310,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -33332,7 +33380,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33376,17 +33424,17 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -33677,24 +33725,24 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K269" s="2" t="inlineStr"/>
       <c r="L269" s="2" t="inlineStr"/>
       <c r="M269" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N269" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O269" s="2" t="inlineStr">
@@ -33704,7 +33752,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33753,12 +33801,12 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -33882,7 +33930,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -33915,32 +33963,36 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K271" s="2" t="inlineStr"/>
       <c r="L271" s="2" t="inlineStr"/>
       <c r="M271" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N271" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N271" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O271" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -33948,7 +34000,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -33972,17 +34024,17 @@
       </c>
       <c r="X271" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y271" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z271" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA271" s="2" t="inlineStr">
@@ -33992,17 +34044,17 @@
       </c>
       <c r="AB271" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -34155,32 +34207,36 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K273" s="2" t="inlineStr"/>
       <c r="L273" s="2" t="inlineStr"/>
       <c r="M273" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N273" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N273" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O273" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -34188,7 +34244,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34212,17 +34268,17 @@
       </c>
       <c r="X273" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y273" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z273" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA273" s="2" t="inlineStr">
@@ -34232,17 +34288,17 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -34275,32 +34331,36 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr"/>
       <c r="M274" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N274" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O274" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -34308,7 +34368,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34332,17 +34392,17 @@
       </c>
       <c r="X274" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z274" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA274" s="2" t="inlineStr">
@@ -34352,17 +34412,17 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -34482,7 +34542,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -34515,32 +34575,36 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr"/>
       <c r="M276" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N276" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N276" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O276" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -34548,7 +34612,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34572,17 +34636,17 @@
       </c>
       <c r="X276" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y276" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z276" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA276" s="2" t="inlineStr">
@@ -34592,12 +34656,12 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
@@ -34635,32 +34699,36 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr"/>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N277" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N277" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O277" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -34668,7 +34736,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34692,17 +34760,17 @@
       </c>
       <c r="X277" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y277" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z277" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA277" s="2" t="inlineStr">
@@ -34712,17 +34780,17 @@
       </c>
       <c r="AB277" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -34755,32 +34823,36 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr"/>
       <c r="M278" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N278" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O278" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -34788,7 +34860,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34812,17 +34884,17 @@
       </c>
       <c r="X278" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z278" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA278" s="2" t="inlineStr">
@@ -34832,17 +34904,17 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -34908,7 +34980,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34952,17 +35024,17 @@
       </c>
       <c r="AB279" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -35028,7 +35100,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35072,12 +35144,12 @@
       </c>
       <c r="AB280" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
